--- a/diseases/d117/2020-2025.xlsx
+++ b/diseases/d117/2020-2025.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +8120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8028,6 +8273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8176,6 +8426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8324,6 +8579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8732,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8620,6 +8885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8768,6 +9038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8916,6 +9191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9064,6 +9344,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9360,6 +9650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9508,6 +9803,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9656,6 +9956,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9804,6 +10109,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9952,6 +10262,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10100,6 +10415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10248,6 +10568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10396,6 +10721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10544,6 +10874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10692,6 +11027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10840,6 +11180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10988,6 +11333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11136,6 +11486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11284,6 +11639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11432,6 +11792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11580,6 +11945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11728,6 +12098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11876,6 +12251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12024,6 +12404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12172,6 +12557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12320,6 +12710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12616,6 +13016,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12764,6 +13169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12912,6 +13322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13060,6 +13475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13208,6 +13628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13356,6 +13781,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13504,6 +13934,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13652,6 +14087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13800,6 +14240,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13948,6 +14393,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14096,6 +14546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14244,6 +14699,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14392,6 +14852,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14540,6 +15005,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14688,6 +15158,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14836,6 +15311,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14984,6 +15464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15132,6 +15617,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15280,6 +15770,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15428,6 +15923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15576,6 +16076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15724,6 +16229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15872,6 +16382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16018,6 +16533,11 @@
       <c r="S105" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">

--- a/diseases/d117/2020-2025.xlsx
+++ b/diseases/d117/2020-2025.xlsx
@@ -765,17 +765,15 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -788,22 +786,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -918,17 +906,15 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -941,22 +927,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1071,17 +1047,15 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1094,22 +1068,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1224,17 +1188,15 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1247,22 +1209,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1377,17 +1329,15 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1400,22 +1350,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1530,17 +1470,15 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1553,22 +1491,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1683,17 +1611,15 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1706,22 +1632,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1836,17 +1752,15 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1859,22 +1773,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1989,17 +1893,15 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2012,22 +1914,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2142,17 +2034,15 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2165,22 +2055,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2295,17 +2175,15 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2318,22 +2196,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2448,17 +2316,15 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2471,22 +2337,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2601,17 +2457,15 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2624,22 +2478,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2754,17 +2598,15 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2777,22 +2619,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2907,17 +2739,15 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2930,22 +2760,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3060,17 +2880,15 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3083,22 +2901,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3213,17 +3021,15 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3236,22 +3042,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3366,17 +3162,15 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3389,22 +3183,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3519,17 +3303,15 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3542,22 +3324,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3672,17 +3444,15 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3695,22 +3465,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3825,17 +3585,15 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3848,22 +3606,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3978,17 +3726,15 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4001,22 +3747,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4131,17 +3867,15 @@
       <c r="O24" t="n">
         <v>0</v>
       </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4154,22 +3888,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4284,17 +4008,15 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4307,22 +4029,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4437,17 +4149,15 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4460,22 +4170,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4590,17 +4290,15 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4613,22 +4311,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4743,17 +4431,15 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
       <c r="Q28" t="n">
         <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4766,22 +4452,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4896,17 +4572,15 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4919,22 +4593,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5049,17 +4713,15 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5072,22 +4734,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5202,17 +4854,15 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5225,22 +4875,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5355,17 +4995,15 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5378,22 +5016,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5508,17 +5136,15 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5531,22 +5157,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5661,17 +5277,15 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5684,22 +5298,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5814,17 +5418,15 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5837,22 +5439,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5967,17 +5559,15 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5990,22 +5580,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6120,17 +5700,15 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6143,22 +5721,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6273,17 +5841,15 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6296,22 +5862,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6426,17 +5982,15 @@
       <c r="O39" t="n">
         <v>0</v>
       </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6449,22 +6003,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6579,17 +6123,15 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6602,22 +6144,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6732,17 +6264,15 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6755,22 +6285,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6885,17 +6405,15 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6908,22 +6426,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
@@ -7038,17 +6546,15 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7061,22 +6567,12 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
-      </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
@@ -7191,17 +6687,15 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7214,22 +6708,12 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
-      </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
@@ -7344,17 +6828,15 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7367,22 +6849,12 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
-      </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
@@ -7497,17 +6969,15 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7520,22 +6990,12 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
-      </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
@@ -7650,17 +7110,15 @@
       <c r="O47" t="n">
         <v>0</v>
       </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7673,22 +7131,12 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
-      </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
@@ -7803,17 +7251,15 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7826,22 +7272,12 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
-      </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
@@ -7956,17 +7392,15 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7979,22 +7413,12 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
@@ -8109,17 +7533,15 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8132,22 +7554,12 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
-      </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
@@ -8262,17 +7674,15 @@
       <c r="O51" t="n">
         <v>0</v>
       </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8285,22 +7695,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
@@ -8415,17 +7815,15 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8438,22 +7836,12 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
-      </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
@@ -8568,17 +7956,15 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
       <c r="Q53" t="n">
         <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8591,22 +7977,12 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
-      </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
@@ -8721,17 +8097,15 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
       <c r="Q54" t="n">
         <v>0</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8744,22 +8118,12 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
-      </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
@@ -8874,17 +8238,15 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8897,22 +8259,12 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
@@ -9027,17 +8379,15 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9050,22 +8400,12 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
-      </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -9180,17 +8520,15 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
       <c r="Q57" t="n">
         <v>0</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9203,22 +8541,12 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
-      </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
@@ -9333,17 +8661,15 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9356,22 +8682,12 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
-      </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -9486,17 +8802,15 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9509,22 +8823,12 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
-      </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -9639,17 +8943,15 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9662,22 +8964,12 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
-      </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -9792,17 +9084,15 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9815,22 +9105,12 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
-      </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -9945,17 +9225,15 @@
       <c r="O62" t="n">
         <v>0</v>
       </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9968,22 +9246,12 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
-      </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -10098,17 +9366,15 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
       <c r="Q63" t="n">
         <v>0</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10121,22 +9387,12 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
-      </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -10251,17 +9507,15 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10274,22 +9528,12 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
-      </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -10404,17 +9648,15 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10427,22 +9669,12 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -10557,17 +9789,15 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10580,22 +9810,12 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -10710,17 +9930,15 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10733,22 +9951,12 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -10863,17 +10071,15 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
       <c r="Q68" t="n">
         <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10886,22 +10092,12 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -11016,17 +10212,15 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11039,22 +10233,12 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
@@ -11169,17 +10353,15 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11192,22 +10374,12 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
@@ -11322,17 +10494,15 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11345,22 +10515,12 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
-      </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -11475,17 +10635,15 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
       <c r="Q72" t="n">
         <v>0</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11498,22 +10656,12 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
-      </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
@@ -11628,17 +10776,15 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11651,22 +10797,12 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
-      </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
@@ -11781,17 +10917,15 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
       <c r="Q74" t="n">
         <v>0</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11804,22 +10938,12 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
-      </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
@@ -11934,17 +11058,15 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11957,22 +11079,12 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -12087,17 +11199,15 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
       <c r="Q76" t="n">
         <v>0</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12110,22 +11220,12 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
-      </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
@@ -12240,17 +11340,15 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12263,22 +11361,12 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
@@ -12393,17 +11481,15 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12416,22 +11502,12 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
-      </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -12546,17 +11622,15 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
       <c r="Q79" t="n">
         <v>0</v>
       </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12569,22 +11643,12 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
@@ -12699,17 +11763,15 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
       <c r="Q80" t="n">
         <v>0</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12722,22 +11784,12 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
-      </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
@@ -12852,17 +11904,15 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
       <c r="Q81" t="n">
         <v>0</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12875,22 +11925,12 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -13005,17 +12045,15 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13028,22 +12066,12 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
@@ -13158,17 +12186,15 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13181,22 +12207,12 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
-      </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
@@ -13311,17 +12327,15 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13334,22 +12348,12 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -13464,17 +12468,15 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13487,22 +12489,12 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
@@ -13617,17 +12609,15 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
       <c r="Q86" t="n">
         <v>0</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13640,22 +12630,12 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
@@ -13770,17 +12750,15 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13793,22 +12771,12 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
-      </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -13923,17 +12891,15 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
       <c r="Q88" t="n">
         <v>0</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13946,22 +12912,12 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
-      </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
@@ -14076,17 +13032,15 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
       <c r="Q89" t="n">
         <v>0</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14099,22 +13053,12 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
-      </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
@@ -14229,17 +13173,15 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14252,22 +13194,12 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
-      </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -14382,17 +13314,15 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
       <c r="Q91" t="n">
         <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14405,22 +13335,12 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
-      </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
@@ -14535,17 +13455,15 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14558,22 +13476,12 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
-      </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
@@ -14688,17 +13596,15 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14711,22 +13617,12 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
-      </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -14841,17 +13737,15 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14864,22 +13758,12 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
-      </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
@@ -14994,17 +13878,15 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15017,22 +13899,12 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
@@ -15147,17 +14019,15 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
+      <c r="P96" t="n">
+        <v>0</v>
+      </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15170,22 +14040,12 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
-      </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -15300,17 +14160,15 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
+      <c r="P97" t="n">
+        <v>0</v>
+      </c>
       <c r="Q97" t="n">
         <v>0</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15323,22 +14181,12 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
@@ -15453,17 +14301,15 @@
       <c r="O98" t="n">
         <v>0</v>
       </c>
+      <c r="P98" t="n">
+        <v>0</v>
+      </c>
       <c r="Q98" t="n">
         <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15476,22 +14322,12 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
-      </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
@@ -15606,17 +14442,15 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15629,22 +14463,12 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -15759,17 +14583,15 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15782,22 +14604,12 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
@@ -15912,17 +14724,15 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
+      <c r="P101" t="n">
+        <v>0</v>
+      </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15935,22 +14745,12 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
-      </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
@@ -16065,17 +14865,15 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
+      <c r="P102" t="n">
+        <v>0</v>
+      </c>
       <c r="Q102" t="n">
         <v>0</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16088,22 +14886,12 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
-      </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -16218,17 +15006,15 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
       <c r="Q103" t="n">
         <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16241,22 +15027,12 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
-      </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
@@ -16371,17 +15147,15 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
       <c r="Q104" t="n">
         <v>0</v>
       </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16394,22 +15168,12 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
@@ -16524,17 +15288,15 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
       <c r="Q105" t="n">
         <v>0</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16547,22 +15309,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
